--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -49,7 +49,7 @@
     <t>这是用例1</t>
   </si>
   <si>
-    <t>test_new_9999</t>
+    <t>test_0006</t>
   </si>
   <si>
     <t>code":"200","msg":"注册成功1</t>
@@ -58,7 +58,7 @@
     <t>这是用例2</t>
   </si>
   <si>
-    <t>test_new_10000</t>
+    <t>test_0007</t>
   </si>
   <si>
     <t>code":"200","msg":"注册成功2</t>
@@ -67,7 +67,7 @@
     <t>这是用例3</t>
   </si>
   <si>
-    <t>test_new_10001</t>
+    <t>test_0008</t>
   </si>
   <si>
     <t>code":"200","msg":"注册成功3</t>
@@ -76,7 +76,7 @@
     <t>这是用例4</t>
   </si>
   <si>
-    <t>test_new_10002</t>
+    <t>test_0009</t>
   </si>
   <si>
     <t>code":"200","msg":"注册成功4</t>
@@ -85,7 +85,7 @@
     <t>这是用例5</t>
   </si>
   <si>
-    <t>test_new_10003</t>
+    <t>test_0010</t>
   </si>
   <si>
     <t>code":"200","msg":"注册成功5</t>
